--- a/karatina/KARATINA DEFINED ARREARS.xlsx
+++ b/karatina/KARATINA DEFINED ARREARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\KashLeo data\karatina\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8CCF129-4887-47D1-9901-4E6EBE317F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C2A943-5A31-48EA-99B7-0CDC167892A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
